--- a/outputs/Validation_Report.xlsx
+++ b/outputs/Validation_Report.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
@@ -511,14 +511,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -536,14 +536,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -561,14 +561,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -586,14 +586,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -636,14 +636,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -661,14 +661,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
@@ -686,14 +686,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
@@ -711,14 +711,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
@@ -736,14 +736,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -811,14 +811,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
@@ -836,14 +836,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
@@ -861,14 +861,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
@@ -886,14 +886,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
@@ -911,14 +911,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
@@ -936,14 +936,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
@@ -961,14 +961,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
@@ -986,14 +986,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
         <v>100</v>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
         <v>100</v>
@@ -1036,14 +1036,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
         <v>100</v>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
@@ -1086,14 +1086,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
@@ -1111,14 +1111,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>25.9</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
@@ -1161,14 +1161,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
@@ -1193,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>71.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="F31" t="n">
         <v>6</v>
@@ -1219,16 +1219,16 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19</v>
+      </c>
+      <c r="E32" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="F32" t="n">
         <v>7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>14</v>
-      </c>
-      <c r="E32" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F32" t="n">
-        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -1269,14 +1269,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E34" t="n">
         <v>100</v>
@@ -1294,14 +1294,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E35" t="n">
         <v>100</v>
@@ -1326,10 +1326,10 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>90.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -1351,10 +1351,10 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E37" t="n">
-        <v>85.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -1369,14 +1369,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
@@ -1398,20 +1398,20 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E39" t="n">
-        <v>85.7</v>
+        <v>81.5</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Iron: 1 outside [0, 500]</t>
+          <t>Iron: 1 outside [0, 500]; Iron: 1 mild outliers</t>
         </is>
       </c>
     </row>
@@ -1423,14 +1423,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E40" t="n">
         <v>100</v>
@@ -1448,14 +1448,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
         <v>100</v>
@@ -1477,16 +1477,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E42" t="n">
-        <v>95.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
@@ -1523,14 +1523,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E44" t="n">
         <v>100</v>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
@@ -1573,14 +1573,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E46" t="n">
         <v>100</v>
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
@@ -1648,14 +1648,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E49" t="n">
         <v>100</v>
@@ -1673,14 +1673,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E51" t="n">
         <v>100</v>
@@ -1723,14 +1723,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E53" t="n">
         <v>100</v>
@@ -1773,14 +1773,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
@@ -1798,14 +1798,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E55" t="n">
         <v>100</v>
@@ -1823,20 +1823,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
-        <v>95.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1848,14 +1848,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E57" t="n">
         <v>100</v>
@@ -1873,14 +1873,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E58" t="n">
         <v>100</v>
@@ -1898,14 +1898,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E59" t="n">
         <v>100</v>
@@ -1923,14 +1923,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E60" t="n">
         <v>100</v>
@@ -1948,14 +1948,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E61" t="n">
         <v>100</v>
@@ -1973,14 +1973,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E62" t="n">
         <v>100</v>
@@ -2002,20 +2002,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E63" t="n">
-        <v>90.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SPAD: 1 outside [0, 80]</t>
+          <t>SPAD: 2 outside [0, 80]</t>
         </is>
       </c>
     </row>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E64" t="n">
         <v>100</v>
@@ -2052,14 +2052,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E65" t="n">
         <v>100</v>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
@@ -2102,14 +2102,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E67" t="n">
         <v>100</v>
@@ -2127,14 +2127,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E68" t="n">
         <v>100</v>
@@ -2152,14 +2152,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E69" t="n">
         <v>100</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E70" t="n">
         <v>100</v>
@@ -2202,14 +2202,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
@@ -2227,14 +2227,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E72" t="n">
         <v>100</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E73" t="n">
         <v>100</v>
@@ -2277,14 +2277,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E74" t="n">
         <v>100</v>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E75" t="n">
         <v>100</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E76" t="n">
         <v>100</v>
@@ -2352,14 +2352,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E77" t="n">
         <v>100</v>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E78" t="n">
-        <v>90.5</v>
+        <v>85.2</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
@@ -2402,14 +2402,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E79" t="n">
         <v>100</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E80" t="n">
         <v>100</v>
@@ -2452,14 +2452,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E81" t="n">
         <v>100</v>
@@ -2477,14 +2477,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
@@ -2502,14 +2502,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E83" t="n">
         <v>100</v>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E84" t="n">
         <v>100</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
@@ -2577,14 +2577,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E86" t="n">
         <v>100</v>
@@ -2602,14 +2602,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
@@ -2627,14 +2627,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E88" t="n">
         <v>100</v>
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E89" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -2677,14 +2677,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E90" t="n">
         <v>100</v>
@@ -2702,14 +2702,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E91" t="n">
         <v>100</v>
@@ -2727,14 +2727,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E92" t="n">
         <v>100</v>
@@ -2752,14 +2752,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -2777,14 +2777,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E94" t="n">
         <v>100</v>
@@ -2802,14 +2802,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E95" t="n">
         <v>100</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -2852,14 +2852,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -2927,14 +2927,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2977,14 +2977,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
@@ -3002,14 +3002,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E103" t="n">
         <v>100</v>
@@ -3027,14 +3027,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E104" t="n">
         <v>100</v>
@@ -3052,14 +3052,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E105" t="n">
         <v>100</v>
@@ -3077,14 +3077,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E106" t="n">
         <v>100</v>
@@ -3102,14 +3102,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
@@ -3127,14 +3127,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E108" t="n">
         <v>100</v>
@@ -3152,14 +3152,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E109" t="n">
         <v>100</v>
@@ -3177,14 +3177,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E110" t="n">
         <v>100</v>
@@ -3202,14 +3202,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E111" t="n">
         <v>100</v>
@@ -3227,14 +3227,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
@@ -3252,14 +3252,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
@@ -3302,14 +3302,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E116" t="n">
         <v>100</v>
@@ -3352,14 +3352,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E117" t="n">
         <v>100</v>
@@ -3377,14 +3377,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -3402,14 +3402,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E119" t="n">
         <v>100</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E120" t="n">
         <v>100</v>
@@ -3452,14 +3452,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
@@ -3502,14 +3502,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
@@ -3552,14 +3552,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E125" t="n">
         <v>100</v>
@@ -3577,14 +3577,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E126" t="n">
         <v>100</v>
@@ -3602,14 +3602,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
@@ -3627,14 +3627,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -3652,14 +3652,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E129" t="n">
         <v>100</v>
@@ -3677,14 +3677,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E130" t="n">
         <v>100</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E131" t="n">
         <v>100</v>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E132" t="n">
         <v>100</v>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E133" t="n">
         <v>100</v>
@@ -3777,14 +3777,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E134" t="n">
         <v>100</v>
@@ -3802,14 +3802,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
@@ -3827,14 +3827,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E136" t="n">
         <v>100</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E137" t="n">
         <v>100</v>
@@ -3877,14 +3877,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E138" t="n">
         <v>100</v>
@@ -3902,14 +3902,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>

--- a/outputs/Validation_Report.xlsx
+++ b/outputs/Validation_Report.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E23" t="n">
         <v>100</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E24" t="n">
         <v>100</v>
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
         <v>100</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>25.9</v>
+        <v>41.2</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
@@ -1190,22 +1190,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
+        <v>46</v>
+      </c>
+      <c r="E31" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F31" t="n">
         <v>21</v>
       </c>
-      <c r="E31" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="F31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Soil_pH: 2 outside [3.0, 10.0]</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1219,22 +1215,18 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="E32" t="n">
-        <v>70.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>EC: 2 outside [0, 20]</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1248,16 +1240,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E33" t="n">
-        <v>96.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
@@ -1276,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E34" t="n">
         <v>100</v>
@@ -1301,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E35" t="n">
         <v>100</v>
@@ -1323,18 +1315,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phosphorus: 1 mild outliers</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1348,16 +1344,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E37" t="n">
-        <v>88.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1376,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
@@ -1398,22 +1394,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>81.5</v>
+        <v>88.2</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Iron: 1 outside [0, 500]; Iron: 1 mild outliers</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1430,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E40" t="n">
         <v>100</v>
@@ -1455,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E41" t="n">
         <v>100</v>
@@ -1477,13 +1469,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E42" t="n">
-        <v>92.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -1505,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
@@ -1530,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E44" t="n">
         <v>100</v>
@@ -1555,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
@@ -1580,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E46" t="n">
         <v>100</v>
@@ -1602,16 +1594,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E47" t="n">
-        <v>40.7</v>
+        <v>39.7</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1627,16 +1619,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="F48" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
@@ -1655,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E49" t="n">
         <v>100</v>
@@ -1680,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
@@ -1705,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E51" t="n">
         <v>100</v>
@@ -1730,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
@@ -1755,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E53" t="n">
         <v>100</v>
@@ -1780,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
@@ -1805,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E55" t="n">
         <v>100</v>
@@ -1830,10 +1822,10 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E56" t="n">
-        <v>92.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -1855,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E57" t="n">
         <v>100</v>
@@ -1880,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E58" t="n">
         <v>100</v>
@@ -1905,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E59" t="n">
         <v>100</v>
@@ -1930,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E60" t="n">
         <v>100</v>
@@ -1955,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E61" t="n">
         <v>100</v>
@@ -1980,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E62" t="n">
         <v>100</v>
@@ -2002,22 +1994,18 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E63" t="n">
-        <v>88.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>SPAD: 2 outside [0, 80]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2034,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E64" t="n">
         <v>100</v>
@@ -2059,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E65" t="n">
         <v>100</v>
@@ -2084,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
@@ -2109,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E67" t="n">
         <v>100</v>
@@ -2134,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E68" t="n">
         <v>100</v>
@@ -2159,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E69" t="n">
         <v>100</v>
@@ -2184,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E70" t="n">
         <v>100</v>
@@ -2209,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
@@ -2234,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E72" t="n">
         <v>100</v>
@@ -2259,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E73" t="n">
         <v>100</v>
@@ -2284,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E74" t="n">
         <v>100</v>
@@ -2309,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E75" t="n">
         <v>100</v>
@@ -2334,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E76" t="n">
         <v>100</v>
@@ -2359,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E77" t="n">
         <v>100</v>
@@ -2381,18 +2369,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E78" t="n">
-        <v>85.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Yield_per_Hectare: 3 mild outliers</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2409,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E79" t="n">
         <v>100</v>
@@ -2434,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E80" t="n">
         <v>100</v>
@@ -2459,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E81" t="n">
         <v>100</v>
@@ -2484,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
@@ -2509,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E83" t="n">
         <v>100</v>
@@ -2534,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E84" t="n">
         <v>100</v>
@@ -2559,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
@@ -2584,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E86" t="n">
         <v>100</v>
@@ -2609,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
@@ -2634,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E88" t="n">
         <v>100</v>
@@ -2659,10 +2651,10 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E89" t="n">
-        <v>96.3</v>
+        <v>98.5</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -2684,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E90" t="n">
         <v>100</v>
@@ -2709,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E91" t="n">
         <v>100</v>
@@ -2734,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E92" t="n">
         <v>100</v>
@@ -2759,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -2784,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E94" t="n">
         <v>100</v>
@@ -2809,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E95" t="n">
         <v>100</v>
@@ -2834,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -2859,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -2884,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -2909,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -2934,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
@@ -2959,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2984,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
@@ -3009,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E103" t="n">
         <v>100</v>
@@ -3034,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E104" t="n">
         <v>100</v>
@@ -3059,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E105" t="n">
         <v>100</v>
@@ -3084,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E106" t="n">
         <v>100</v>
@@ -3109,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
@@ -3134,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E108" t="n">
         <v>100</v>
@@ -3159,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E109" t="n">
         <v>100</v>
@@ -3184,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E110" t="n">
         <v>100</v>
@@ -3209,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E111" t="n">
         <v>100</v>
@@ -3234,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
@@ -3259,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
@@ -3284,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
@@ -3309,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
@@ -3334,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E116" t="n">
         <v>100</v>
@@ -3359,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E117" t="n">
         <v>100</v>
@@ -3384,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -3409,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E119" t="n">
         <v>100</v>
@@ -3434,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E120" t="n">
         <v>100</v>
@@ -3459,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
@@ -3484,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
@@ -3509,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -3534,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
@@ -3559,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E125" t="n">
         <v>100</v>
@@ -3584,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E126" t="n">
         <v>100</v>
@@ -3609,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
@@ -3634,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -3659,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E129" t="n">
         <v>100</v>
@@ -3684,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E130" t="n">
         <v>100</v>
@@ -3709,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E131" t="n">
         <v>100</v>
@@ -3734,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E132" t="n">
         <v>100</v>
@@ -3759,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E133" t="n">
         <v>100</v>
@@ -3784,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E134" t="n">
         <v>100</v>
@@ -3809,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
@@ -3834,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E136" t="n">
         <v>100</v>
@@ -3859,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E137" t="n">
         <v>100</v>
@@ -3884,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E138" t="n">
         <v>100</v>
@@ -3909,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>

--- a/outputs/Validation_Report.xlsx
+++ b/outputs/Validation_Report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
@@ -511,14 +511,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -536,14 +536,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -561,14 +561,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -586,14 +586,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -606,44 +606,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Crop</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scientific_Name</t>
+          <t>Institution</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -656,44 +656,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Variety</t>
+          <t>Crop</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Scientific_Name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
@@ -706,19 +706,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Growth_Duration_Days</t>
+          <t>Variety</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
@@ -731,19 +731,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Growth_Stage</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
@@ -756,69 +756,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Growth_Duration_Days</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Replications</t>
+          <t>Growth_Stage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plot_Size</t>
+          <t>Cover_Crop</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
@@ -831,19 +831,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spacing_Row</t>
+          <t>Previous_Crop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
@@ -856,19 +856,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spacing_Plant</t>
+          <t>Intercrop_Name</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
@@ -881,69 +881,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sample_Size</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Replications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Plot_Size</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
@@ -956,19 +956,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Spacing_Row</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
@@ -981,19 +981,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Spacing_Plant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>100</v>
@@ -1006,19 +1006,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Sample_Size</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
         <v>100</v>
@@ -1031,19 +1031,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Altitude</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>100</v>
@@ -1056,19 +1056,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Temperature_Max</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
@@ -1081,19 +1081,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Temperature_Min</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
@@ -1106,19 +1106,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Average_Temperature</t>
+          <t>Plot_ID</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
@@ -1131,44 +1131,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rainfall</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>41.2</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Humidity</t>
+          <t>Experiment_Objective</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
@@ -1181,94 +1181,94 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Soil_pH</t>
+          <t>Sowing_Date</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>67.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Harvest_Date</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>77.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Organic_Carbon</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Organic_Matter</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
         <v>100</v>
@@ -1281,19 +1281,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Altitude</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>100</v>
@@ -1306,73 +1306,69 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phosphorus</t>
+          <t>Temperature_Max</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Phosphorus: 1 mild outliers</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Potassium</t>
+          <t>Temperature_Min</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sulphur</t>
+          <t>Average_Temperature</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
@@ -1385,44 +1381,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Rainfall</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
         <v>8</v>
       </c>
-      <c r="D39" t="n">
-        <v>60</v>
-      </c>
       <c r="E39" t="n">
-        <v>88.2</v>
+        <v>80</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Humidity</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>100</v>
@@ -1435,19 +1431,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Solar_Radiation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
         <v>100</v>
@@ -1460,44 +1456,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Wind_Speed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Calcium</t>
+          <t>ET0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
@@ -1510,19 +1506,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Magnesium</t>
+          <t>Climate_Zone</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
         <v>100</v>
@@ -1535,7 +1531,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Boron</t>
+          <t>Soil_pH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1544,23 +1540,23 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1569,85 +1565,93 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>EC: 1 outside [0, 20]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Organic_Carbon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>39.7</v>
+        <v>90</v>
       </c>
       <c r="F47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Organic_Carbon: 1 outside [0, 10]</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Fertilizer_Name</t>
+          <t>Organic_Matter</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
-        <v>4.4</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Organic_Fertilizer</t>
+          <t>Nitrogen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
         <v>100</v>
@@ -1660,19 +1664,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biofertilizer</t>
+          <t>Phosphorus</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
@@ -1685,19 +1689,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Potassium</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
         <v>100</v>
@@ -1710,19 +1714,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application_Method</t>
+          <t>Sulphur</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
@@ -1735,7 +1739,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application_Interval</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1744,35 +1748,39 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Iron: 1 outside [0, 500]; Iron: 1 mild outliers</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Shoot_Length_cm</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
@@ -1785,19 +1793,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Root_Length_cm</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
         <v>100</v>
@@ -1810,7 +1818,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1819,35 +1827,39 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>97.09999999999999</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Zinc: 1 outside [0, 100]; Zinc: 1 mild outliers</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>Calcium</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
         <v>100</v>
@@ -1860,19 +1872,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Root_Biomass_g</t>
+          <t>Magnesium</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E58" t="n">
         <v>100</v>
@@ -1885,19 +1897,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Leaf_Area_cm2</t>
+          <t>Boron</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
         <v>100</v>
@@ -1910,19 +1922,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Leaf_Number</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
         <v>100</v>
@@ -1935,19 +1947,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tillers</t>
+          <t>Sodium</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
         <v>100</v>
@@ -1960,19 +1972,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Root_Diameter_mm</t>
+          <t>Chlorine</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
         <v>100</v>
@@ -1985,44 +1997,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Moisture_Content</t>
+          <t>Soil_Bulk_Density</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
         <v>100</v>
@@ -2035,19 +2047,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dry_Matter</t>
+          <t>Soil_Clay_Pct</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E65" t="n">
         <v>100</v>
@@ -2060,19 +2072,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Stem_Diameter_mm</t>
+          <t>Soil_Silt_Pct</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
@@ -2085,19 +2097,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Branches</t>
+          <t>Soil_Sand_Pct</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
         <v>100</v>
@@ -2110,19 +2122,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>Soil_Texture</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
         <v>100</v>
@@ -2135,19 +2147,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Flowers</t>
+          <t>Soil_Class</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
         <v>100</v>
@@ -2160,19 +2172,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Plant_Height_30_cm</t>
+          <t>Soil_Depth_cm</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E70" t="n">
         <v>100</v>
@@ -2185,69 +2197,69 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Plant_Height_60_cm</t>
+          <t>Treatment</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Plant_Height_90_cm</t>
+          <t>Fertilizer_Name</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Leaf_Area_30_cm2</t>
+          <t>Organic_Fertilizer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
         <v>100</v>
@@ -2260,19 +2272,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leaf_Area_60_cm2</t>
+          <t>Biofertilizer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E74" t="n">
         <v>100</v>
@@ -2285,19 +2297,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Leaf_Area_90_cm2</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
         <v>100</v>
@@ -2310,19 +2322,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Yield_per_Plot</t>
+          <t>Application_Method</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
         <v>100</v>
@@ -2335,19 +2347,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Yield_per_Acre</t>
+          <t>Application_Interval</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E77" t="n">
         <v>100</v>
@@ -2360,48 +2372,44 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Yield_per_Hectare</t>
+          <t>Fertilizer_Calcium</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>79.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>13</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Yield_per_Hectare: 3 mild outliers</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fruit_Number</t>
+          <t>Fertilizer_Magnesium</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
         <v>100</v>
@@ -2414,19 +2422,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fruit_Weight</t>
+          <t>Fertilizer_Boron</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
         <v>100</v>
@@ -2439,19 +2447,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fruit_Diameter_mm</t>
+          <t>Fertilizer_Chlorine</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E81" t="n">
         <v>100</v>
@@ -2464,19 +2472,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Spike_Length</t>
+          <t>Fertilizer_Molybdenum</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
@@ -2489,19 +2497,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Seeds_per_Spike</t>
+          <t>Shoot_Length_cm</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
         <v>100</v>
@@ -2514,19 +2522,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>100_Seed_Weight</t>
+          <t>Root_Length_cm</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E84" t="n">
         <v>100</v>
@@ -2539,19 +2547,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Root_Weight</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
@@ -2564,19 +2572,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pod_Weight</t>
+          <t>Shoot_Biomass_g</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E86" t="n">
         <v>100</v>
@@ -2589,19 +2597,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Harvest_Index</t>
+          <t>Root_Biomass_g</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
@@ -2614,19 +2622,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Biomass_Yield</t>
+          <t>Leaf_Area_cm2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
         <v>100</v>
@@ -2639,44 +2647,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Protein</t>
+          <t>Leaf_Number</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ash</t>
+          <t>Tillers</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E90" t="n">
         <v>100</v>
@@ -2689,19 +2697,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gluten</t>
+          <t>Root_Diameter_mm</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E91" t="n">
         <v>100</v>
@@ -2714,19 +2722,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Fiber</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E92" t="n">
         <v>100</v>
@@ -2739,19 +2747,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Carbohydrates</t>
+          <t>Moisture_Content</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -2764,19 +2772,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fat</t>
+          <t>Dry_Matter</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E94" t="n">
         <v>100</v>
@@ -2789,19 +2797,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nitrogen_Content</t>
+          <t>Stem_Diameter_mm</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
         <v>100</v>
@@ -2814,19 +2822,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Phosphorus_Content</t>
+          <t>Branches</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -2839,19 +2847,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Potassium_Content</t>
+          <t>Nodes</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -2864,19 +2872,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Iron_Content</t>
+          <t>Flowers</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -2889,19 +2897,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Copper_Content</t>
+          <t>Plant_Height_30_cm</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -2914,19 +2922,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Zinc_Content</t>
+          <t>Plant_Height_60_cm</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
@@ -2939,19 +2947,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Manganese_Content</t>
+          <t>Plant_Height_90_cm</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2964,19 +2972,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sulphur_Content</t>
+          <t>Plant_Height_120_cm</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
@@ -2989,19 +2997,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Target_Yield</t>
+          <t>Leaf_Area_30_cm2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E103" t="n">
         <v>100</v>
@@ -3014,19 +3022,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Target_Fertilizer</t>
+          <t>Leaf_Area_60_cm2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E104" t="n">
         <v>100</v>
@@ -3039,19 +3047,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Target_Nitrogen</t>
+          <t>Leaf_Area_90_cm2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E105" t="n">
         <v>100</v>
@@ -3064,19 +3072,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Target_Phosphorus</t>
+          <t>Leaf_Area_120_cm2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E106" t="n">
         <v>100</v>
@@ -3089,19 +3097,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Target_Potassium</t>
+          <t>Branches_60</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
@@ -3114,19 +3122,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Growing_Degree_Days</t>
+          <t>Branches_90</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E108" t="n">
         <v>100</v>
@@ -3139,19 +3147,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Heat_Units</t>
+          <t>Flowers_60</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E109" t="n">
         <v>100</v>
@@ -3164,19 +3172,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Harvest_Index_Calc</t>
+          <t>Yield_per_Plot</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
         <v>100</v>
@@ -3189,19 +3197,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Nitrogen_Use_Efficiency</t>
+          <t>Yield_per_Acre</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E111" t="n">
         <v>100</v>
@@ -3214,7 +3222,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Water_Use_Efficiency</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3223,35 +3231,35 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Rainfall_Anomaly</t>
+          <t>Fruit_Number</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
@@ -3264,19 +3272,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Stress_Index</t>
+          <t>Fruit_Weight</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
@@ -3289,19 +3297,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Disease_Risk_Index</t>
+          <t>Fruit_Diameter_mm</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
@@ -3314,19 +3322,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Yield_per_Plant</t>
+          <t>Spike_Length</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E116" t="n">
         <v>100</v>
@@ -3339,19 +3347,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Yield_per_Plot_Calc</t>
+          <t>Seeds_per_Spike</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E117" t="n">
         <v>100</v>
@@ -3364,19 +3372,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Yield_per_Hectare_Calc</t>
+          <t>100_Seed_Weight</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -3389,19 +3397,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Temp_x_Rainfall</t>
+          <t>Root_Weight</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E119" t="n">
         <v>100</v>
@@ -3414,19 +3422,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>N_x_P</t>
+          <t>Pod_Weight</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E120" t="n">
         <v>100</v>
@@ -3439,19 +3447,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Temp_ squared</t>
+          <t>Harvest_Index</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
@@ -3464,19 +3472,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Rainfall_7d_MA</t>
+          <t>Biomass_Yield</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
@@ -3489,19 +3497,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Temp_7d_MA</t>
+          <t>FruitWeight_90_g</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -3514,19 +3522,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Feature_Available_Before_Prediction</t>
+          <t>FruitWeight_120_g</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
@@ -3539,19 +3547,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Crop_Code</t>
+          <t>FruitDiameter_90_mm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
         <v>100</v>
@@ -3564,19 +3572,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Season_Code</t>
+          <t>FruitDiameter_120_mm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E126" t="n">
         <v>100</v>
@@ -3589,19 +3597,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Variety_Code</t>
+          <t>YieldPlot_90_g</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
@@ -3614,19 +3622,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fertilizer_Code</t>
+          <t>YieldPlot_120_g</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -3639,19 +3647,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Soil_Texture_Code</t>
+          <t>Yield_13pct_Moisture</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E129" t="n">
         <v>100</v>
@@ -3664,19 +3672,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Country_Code</t>
+          <t>Marketable_Yield</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E130" t="n">
         <v>100</v>
@@ -3689,19 +3697,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Predicted_Yield</t>
+          <t>Biological_Yield</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E131" t="n">
         <v>100</v>
@@ -3714,19 +3722,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Expected_Biomass</t>
+          <t>Stover_Yield</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E132" t="n">
         <v>100</v>
@@ -3739,19 +3747,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Expected_Plant_Height</t>
+          <t>Seed_Yield</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E133" t="n">
         <v>100</v>
@@ -3764,19 +3772,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Recommended_Fertilizer</t>
+          <t>Pods_Number</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E134" t="n">
         <v>100</v>
@@ -3789,19 +3797,19 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Recommended_Dose</t>
+          <t>Seeds_per_Pod</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
@@ -3814,19 +3822,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Recommended_Application_Interval</t>
+          <t>Weed_Biomass</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E136" t="n">
         <v>100</v>
@@ -3839,7 +3847,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Expected_Yield_Increase</t>
+          <t>Protein</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3848,35 +3856,35 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="E137" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Confidence_Score</t>
+          <t>Ash</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E138" t="n">
         <v>100</v>
@@ -3889,27 +3897,3977 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Gluten</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>10</v>
+      </c>
+      <c r="E139" t="n">
+        <v>100</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Fiber</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>10</v>
+      </c>
+      <c r="E140" t="n">
+        <v>100</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Carbohydrates</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>10</v>
+      </c>
+      <c r="E141" t="n">
+        <v>100</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Fat</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>10</v>
+      </c>
+      <c r="E142" t="n">
+        <v>100</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Nitrogen_Content</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>10</v>
+      </c>
+      <c r="E143" t="n">
+        <v>100</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Phosphorus_Content</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>10</v>
+      </c>
+      <c r="E144" t="n">
+        <v>100</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Potassium_Content</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>10</v>
+      </c>
+      <c r="E145" t="n">
+        <v>100</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Iron_Content</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" t="n">
+        <v>100</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Copper_Content</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>10</v>
+      </c>
+      <c r="E147" t="n">
+        <v>100</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Zinc_Content</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>10</v>
+      </c>
+      <c r="E148" t="n">
+        <v>100</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Manganese_Content</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>10</v>
+      </c>
+      <c r="E149" t="n">
+        <v>100</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sulphur_Content</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" t="n">
+        <v>100</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Calcium_Content</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>10</v>
+      </c>
+      <c r="E151" t="n">
+        <v>100</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Magnesium_Content</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>10</v>
+      </c>
+      <c r="E152" t="n">
+        <v>100</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Boron_Content</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>10</v>
+      </c>
+      <c r="E153" t="n">
+        <v>100</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Chlorine_Content</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="n">
+        <v>100</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Molybdenum_Content</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" t="n">
+        <v>100</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Starch</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" t="n">
+        <v>100</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" t="n">
+        <v>100</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Target_Yield</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>10</v>
+      </c>
+      <c r="E158" t="n">
+        <v>100</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Target_Fertilizer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>10</v>
+      </c>
+      <c r="E159" t="n">
+        <v>100</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Target_Nitrogen</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" t="n">
+        <v>100</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Target_Phosphorus</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>10</v>
+      </c>
+      <c r="E161" t="n">
+        <v>100</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Target_Potassium</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>10</v>
+      </c>
+      <c r="E162" t="n">
+        <v>100</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Growing_Degree_Days</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>10</v>
+      </c>
+      <c r="E163" t="n">
+        <v>100</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Heat_Units</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>10</v>
+      </c>
+      <c r="E164" t="n">
+        <v>100</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Harvest_Index_Calc</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>10</v>
+      </c>
+      <c r="E165" t="n">
+        <v>100</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nitrogen_Use_Efficiency</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>10</v>
+      </c>
+      <c r="E166" t="n">
+        <v>100</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Water_Use_Efficiency</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>10</v>
+      </c>
+      <c r="E167" t="n">
+        <v>100</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Rainfall_Anomaly</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>10</v>
+      </c>
+      <c r="E168" t="n">
+        <v>100</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Stress_Index</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>10</v>
+      </c>
+      <c r="E169" t="n">
+        <v>100</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Disease_Risk_Index</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>10</v>
+      </c>
+      <c r="E170" t="n">
+        <v>100</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Yield_per_Plant</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>10</v>
+      </c>
+      <c r="E171" t="n">
+        <v>100</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Yield_per_Plot_Calc</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>10</v>
+      </c>
+      <c r="E172" t="n">
+        <v>100</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Yield_per_Hectare_Calc</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>10</v>
+      </c>
+      <c r="E173" t="n">
+        <v>100</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Temp_x_Rainfall</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>10</v>
+      </c>
+      <c r="E174" t="n">
+        <v>100</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>N_x_P</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>10</v>
+      </c>
+      <c r="E175" t="n">
+        <v>100</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Temp_squared</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>10</v>
+      </c>
+      <c r="E176" t="n">
+        <v>100</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Rainfall_7d_MA</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>10</v>
+      </c>
+      <c r="E177" t="n">
+        <v>100</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Temp_7d_MA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>10</v>
+      </c>
+      <c r="E178" t="n">
+        <v>100</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Feature_Available_Before_Prediction</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>10</v>
+      </c>
+      <c r="E179" t="n">
+        <v>100</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Crop_Code</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>10</v>
+      </c>
+      <c r="E180" t="n">
+        <v>100</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Season_Code</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" t="n">
+        <v>100</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Variety_Code</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>10</v>
+      </c>
+      <c r="E182" t="n">
+        <v>100</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Fertilizer_Code</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>10</v>
+      </c>
+      <c r="E183" t="n">
+        <v>100</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Soil_Texture_Code</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" t="n">
+        <v>100</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Country_Code</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>10</v>
+      </c>
+      <c r="E185" t="n">
+        <v>100</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Predicted_Yield</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>10</v>
+      </c>
+      <c r="E186" t="n">
+        <v>100</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Expected_Biomass</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>10</v>
+      </c>
+      <c r="E187" t="n">
+        <v>100</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Expected_Plant_Height</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>10</v>
+      </c>
+      <c r="E188" t="n">
+        <v>100</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Recommended_Fertilizer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" t="n">
+        <v>100</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Recommended_Dose</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" t="n">
+        <v>100</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Recommended_Application_Interval</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="n">
+        <v>100</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Expected_Yield_Increase</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="n">
+        <v>100</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Confidence_Score</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+      <c r="E193" t="n">
+        <v>100</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>Recommendation_Summary</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="n">
-        <v>68</v>
-      </c>
-      <c r="E139" t="n">
-        <v>100</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="n">
+        <v>100</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SOC_Mineralization</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>10</v>
+      </c>
+      <c r="E195" t="n">
+        <v>100</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Residue_C_Decomposition</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>10</v>
+      </c>
+      <c r="E196" t="n">
+        <v>100</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Potential_Evapotranspiration</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>10</v>
+      </c>
+      <c r="E197" t="n">
+        <v>100</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Soil_Moisture</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>10</v>
+      </c>
+      <c r="E198" t="n">
+        <v>100</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Soil_Nitrate_N</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>10</v>
+      </c>
+      <c r="E199" t="n">
+        <v>100</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Soil_Ammonium_N</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>10</v>
+      </c>
+      <c r="E200" t="n">
+        <v>100</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Soil_Available_K</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>10</v>
+      </c>
+      <c r="E201" t="n">
+        <v>100</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Soil_POC</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>10</v>
+      </c>
+      <c r="E202" t="n">
+        <v>100</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Soil_DOC</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>10</v>
+      </c>
+      <c r="E203" t="n">
+        <v>100</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Soil_LOC</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>10</v>
+      </c>
+      <c r="E204" t="n">
+        <v>100</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Soil_MBC</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>10</v>
+      </c>
+      <c r="E205" t="n">
+        <v>100</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Soil_MBN</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>10</v>
+      </c>
+      <c r="E206" t="n">
+        <v>100</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Soil_Carbon_Walkley_Black</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>10</v>
+      </c>
+      <c r="E207" t="n">
+        <v>100</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Soil_Nitrogen_Kjeldahl</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>10</v>
+      </c>
+      <c r="E208" t="n">
+        <v>100</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Soil_Nitrogen_Alkaline_Permanganate</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>10</v>
+      </c>
+      <c r="E209" t="n">
+        <v>100</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Soil_Sulphur_Available</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>10</v>
+      </c>
+      <c r="E210" t="n">
+        <v>100</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Soil_Sulphur_Mehlich3</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>10</v>
+      </c>
+      <c r="E211" t="n">
+        <v>100</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Soil_NO3</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>10</v>
+      </c>
+      <c r="E212" t="n">
+        <v>100</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Soil_NH4</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>10</v>
+      </c>
+      <c r="E213" t="n">
+        <v>100</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Soil_N_Parco2020</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>10</v>
+      </c>
+      <c r="E214" t="n">
+        <v>100</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Soil_N_DeSilva2008</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>10</v>
+      </c>
+      <c r="E215" t="n">
+        <v>100</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Soil_Ca_Ammonium_Acetate</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>10</v>
+      </c>
+      <c r="E216" t="n">
+        <v>100</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Soil_Mg_Ammonium_Acetate</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>10</v>
+      </c>
+      <c r="E217" t="n">
+        <v>100</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Soil_K_Ammonium_Acetate</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>10</v>
+      </c>
+      <c r="E218" t="n">
+        <v>100</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Soil_Glucosidase</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>10</v>
+      </c>
+      <c r="E219" t="n">
+        <v>100</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Soil_Xylosidase</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>10</v>
+      </c>
+      <c r="E220" t="n">
+        <v>100</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Soil_Cellobiosidase</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>10</v>
+      </c>
+      <c r="E221" t="n">
+        <v>100</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Beta_Glucosidase</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>10</v>
+      </c>
+      <c r="E222" t="n">
+        <v>100</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Peroxidase</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>10</v>
+      </c>
+      <c r="E223" t="n">
+        <v>100</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Polyphenol_Oxidase</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>10</v>
+      </c>
+      <c r="E224" t="n">
+        <v>100</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>N_Acetyl_Glucosaminidase</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>10</v>
+      </c>
+      <c r="E225" t="n">
+        <v>100</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Leucine_Aminopeptidase</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>10</v>
+      </c>
+      <c r="E226" t="n">
+        <v>100</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Phosphatase</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>10</v>
+      </c>
+      <c r="E227" t="n">
+        <v>100</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Catalase</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10</v>
+      </c>
+      <c r="E228" t="n">
+        <v>100</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Urease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>10</v>
+      </c>
+      <c r="E229" t="n">
+        <v>100</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Dehydrogenase</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>10</v>
+      </c>
+      <c r="E230" t="n">
+        <v>100</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Bacterial_Diversity_Chao1</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>10</v>
+      </c>
+      <c r="E231" t="n">
+        <v>100</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Bacterial_Diversity_Shannon</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>10</v>
+      </c>
+      <c r="E232" t="n">
+        <v>100</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Fungal_Diversity_Chao1</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>10</v>
+      </c>
+      <c r="E233" t="n">
+        <v>100</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Fungal_Diversity_Shannon</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>10</v>
+      </c>
+      <c r="E234" t="n">
+        <v>100</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Total_PLFAs</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>10</v>
+      </c>
+      <c r="E235" t="n">
+        <v>100</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Gram_Positive_PLFAs</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>10</v>
+      </c>
+      <c r="E236" t="n">
+        <v>100</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Gram_Negative_PLFAs</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>10</v>
+      </c>
+      <c r="E237" t="n">
+        <v>100</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Fungal_PLFAs</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>10</v>
+      </c>
+      <c r="E238" t="n">
+        <v>100</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Bacterial_PLFAs</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>10</v>
+      </c>
+      <c r="E239" t="n">
+        <v>100</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Actinomycetes_PLFAs</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>10</v>
+      </c>
+      <c r="E240" t="n">
+        <v>100</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>NDVI</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>10</v>
+      </c>
+      <c r="E241" t="n">
+        <v>100</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>EVI</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>10</v>
+      </c>
+      <c r="E242" t="n">
+        <v>100</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SAVI</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>10</v>
+      </c>
+      <c r="E243" t="n">
+        <v>100</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>NDWI</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>10</v>
+      </c>
+      <c r="E244" t="n">
+        <v>100</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>NDRE</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>10</v>
+      </c>
+      <c r="E245" t="n">
+        <v>100</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Canopy_Temperature</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>10</v>
+      </c>
+      <c r="E246" t="n">
+        <v>100</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CIG</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>10</v>
+      </c>
+      <c r="E247" t="n">
+        <v>100</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CIRE</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>10</v>
+      </c>
+      <c r="E248" t="n">
+        <v>100</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Calcium_Mehlich3</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>10</v>
+      </c>
+      <c r="E249" t="n">
+        <v>100</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Calcium_Saturation</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>10</v>
+      </c>
+      <c r="E250" t="n">
+        <v>100</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Magnesium_Saturation</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>10</v>
+      </c>
+      <c r="E251" t="n">
+        <v>100</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sodium_Saturation</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>10</v>
+      </c>
+      <c r="E252" t="n">
+        <v>100</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Potassium_Saturation</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>10</v>
+      </c>
+      <c r="E253" t="n">
+        <v>100</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Hydrogen_Saturation</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>10</v>
+      </c>
+      <c r="E254" t="n">
+        <v>100</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Water_Extractable_Nitrate</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>10</v>
+      </c>
+      <c r="E255" t="n">
+        <v>100</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Water_Extractable_Organic_Carbon</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>10</v>
+      </c>
+      <c r="E256" t="n">
+        <v>100</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Water_Extractable_Organic_Nitrogen</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>10</v>
+      </c>
+      <c r="E257" t="n">
+        <v>100</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Water_Extractable_NH4</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>10</v>
+      </c>
+      <c r="E258" t="n">
+        <v>100</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Water_Extractable_CN_Ratio</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>10</v>
+      </c>
+      <c r="E259" t="n">
+        <v>100</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Aggregate_Stability</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>10</v>
+      </c>
+      <c r="E260" t="n">
+        <v>100</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Soil_Respiration</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>10</v>
+      </c>
+      <c r="E261" t="n">
+        <v>100</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Infiltration_Rate</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>10</v>
+      </c>
+      <c r="E262" t="n">
+        <v>100</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Nematode_Maturity_Index</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>10</v>
+      </c>
+      <c r="E263" t="n">
+        <v>100</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Nematode_Plant_Parasitic_Index</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>10</v>
+      </c>
+      <c r="E264" t="n">
+        <v>100</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Nematode_Channel_Index</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>10</v>
+      </c>
+      <c r="E265" t="n">
+        <v>100</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Nematode_Basal_Index</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>10</v>
+      </c>
+      <c r="E266" t="n">
+        <v>100</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Nematode_Enrichment_Index</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>10</v>
+      </c>
+      <c r="E267" t="n">
+        <v>100</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Nematode_Structure_Index</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>10</v>
+      </c>
+      <c r="E268" t="n">
+        <v>100</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Nematode_Total_Biomass_mg</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>10</v>
+      </c>
+      <c r="E269" t="n">
+        <v>100</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Total_Cost</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>10</v>
+      </c>
+      <c r="E270" t="n">
+        <v>100</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Total_Return</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>10</v>
+      </c>
+      <c r="E271" t="n">
+        <v>100</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Net_Profit</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>10</v>
+      </c>
+      <c r="E272" t="n">
+        <v>100</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Benefit_Cost_Ratio</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>10</v>
+      </c>
+      <c r="E273" t="n">
+        <v>100</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>System_Benefit_USD_ha</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>10</v>
+      </c>
+      <c r="E274" t="n">
+        <v>100</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Off_Season_Contribution_Pct</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>10</v>
+      </c>
+      <c r="E275" t="n">
+        <v>100</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>System_Water_Use_Efficiency</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>10</v>
+      </c>
+      <c r="E276" t="n">
+        <v>100</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Phosphorus_Uptake</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>10</v>
+      </c>
+      <c r="E277" t="n">
+        <v>100</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Nitrogen_Uptake</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>10</v>
+      </c>
+      <c r="E278" t="n">
+        <v>100</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Potassium_Uptake</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>10</v>
+      </c>
+      <c r="E279" t="n">
+        <v>100</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sulphur_Uptake</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>10</v>
+      </c>
+      <c r="E280" t="n">
+        <v>100</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Calcium_Uptake</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>10</v>
+      </c>
+      <c r="E281" t="n">
+        <v>100</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Magnesium_Uptake</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>10</v>
+      </c>
+      <c r="E282" t="n">
+        <v>100</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Boron_Uptake</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>10</v>
+      </c>
+      <c r="E283" t="n">
+        <v>100</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Chlorine_Uptake</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>10</v>
+      </c>
+      <c r="E284" t="n">
+        <v>100</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Copper_Uptake</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>10</v>
+      </c>
+      <c r="E285" t="n">
+        <v>100</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Iron_Uptake</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D286" t="n">
+        <v>10</v>
+      </c>
+      <c r="E286" t="n">
+        <v>100</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Manganese_Uptake</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>10</v>
+      </c>
+      <c r="E287" t="n">
+        <v>100</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Molybdenum_Uptake</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" t="n">
+        <v>10</v>
+      </c>
+      <c r="E288" t="n">
+        <v>100</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Zinc_Uptake</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>10</v>
+      </c>
+      <c r="E289" t="n">
+        <v>100</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Irrigation_Method</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>10</v>
+      </c>
+      <c r="E290" t="n">
+        <v>100</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Irrigation_mm</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>10</v>
+      </c>
+      <c r="E291" t="n">
+        <v>100</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sowing_Density</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>10</v>
+      </c>
+      <c r="E292" t="n">
+        <v>100</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Harvest_Density</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>10</v>
+      </c>
+      <c r="E293" t="n">
+        <v>100</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Cultivation_Method</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" t="n">
+        <v>10</v>
+      </c>
+      <c r="E294" t="n">
+        <v>100</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>N_Fixation</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>10</v>
+      </c>
+      <c r="E295" t="n">
+        <v>100</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Soil_pH_CaCl2</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>10</v>
+      </c>
+      <c r="E296" t="n">
+        <v>100</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Soil_pH_KCl</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>10</v>
+      </c>
+      <c r="E297" t="n">
+        <v>100</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
